--- a/TestCases/TC01_CDS_phs002050_RefGen_GRCh37_Platform-Illumina_LibSrc-Genomic.xlsx
+++ b/TestCases/TC01_CDS_phs002050_RefGen_GRCh37_Platform-Illumina_LibSrc-Genomic.xlsx
@@ -542,10 +542,6 @@
           <t>dismiss_popup</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>Dismiss warning popup</t>
@@ -571,8 +567,6 @@
           <t>CDS_Data-Btn</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>Click Data nav button</t>
@@ -598,8 +592,6 @@
           <t>Data_page/Filter/StudyFacet/PHS_Accession/PHS_Accession_Ddn</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>Expand phs filter</t>
@@ -625,7 +617,6 @@
           <t>Data_page/Filter/StudyFacet/PHS_Accession/phs002050_Chkbx</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>phs=phs002050</t>
@@ -656,8 +647,6 @@
           <t>Data_page/Filter/GenomicFacet/ReferenceGenomeAssembly/Ref_Gen_Assembly_Ddn</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>Expand reference_genome filter</t>
@@ -683,7 +672,6 @@
           <t>Data_page/Filter/GenomicFacet/ReferenceGenomeAssembly/GRCh37_Chkbx</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
           <t>reference_genome=GRCh37</t>
@@ -714,8 +702,6 @@
           <t>Data_page/Filter/GenomicFacet/Platform/platform_Ddn</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>Expand platform filter</t>
@@ -738,10 +724,9 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Data_page/Filter/GenomicFacet/Platform/Illumina_Chkbx</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Data_page/Filter/GenomicFacet/Platform/ILLUMINA-Chkbx</t>
+        </is>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>platform=Illumina</t>
@@ -772,8 +757,6 @@
           <t>Data_page/Filter/GenomicFacet/LibrarySource/LibrarySourceMolecule_Ddn</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>Expand library_source filter</t>
@@ -799,7 +782,6 @@
           <t>Data_page/Filter/GenomicFacet/LibrarySource/Genomic_Chkbx</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
           <t>library_source=Genomic</t>
@@ -820,14 +802,11 @@
           <t>read_stat_bar</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>CDS</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>Read stat bar counts</t>
@@ -843,14 +822,11 @@
           <t>multi_function</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>ParticipantsTab</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>Compare ParticipantsTab</t>
@@ -866,14 +842,11 @@
           <t>multi_function</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>SamplesTab</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>Compare SamplesTab</t>
@@ -889,14 +862,11 @@
           <t>multi_function</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>FilesTab</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>Compare FilesTab</t>
